--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902557</v>
+        <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,7 +827,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599750</v>
+        <v>599600</v>
       </c>
       <c r="R3" t="n">
-        <v>6923919</v>
+        <v>6923972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902196</v>
+        <v>124902557</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,14 +946,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599743</v>
+        <v>599750</v>
       </c>
       <c r="R4" t="n">
-        <v>6923891</v>
+        <v>6923919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901243</v>
+        <v>124902196</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1063,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599600</v>
+        <v>599743</v>
       </c>
       <c r="R5" t="n">
-        <v>6923972</v>
+        <v>6923891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902430</v>
+        <v>124902557</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599723</v>
+        <v>599750</v>
       </c>
       <c r="R2" t="n">
-        <v>6923906</v>
+        <v>6923919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124901243</v>
+        <v>124902430</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +804,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599600</v>
+        <v>599723</v>
       </c>
       <c r="R3" t="n">
-        <v>6923972</v>
+        <v>6923906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902557</v>
+        <v>124902196</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -946,10 +941,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599750</v>
+        <v>599743</v>
       </c>
       <c r="R4" t="n">
-        <v>6923919</v>
+        <v>6923891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902196</v>
+        <v>124901243</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1045,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,14 +1062,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599743</v>
+        <v>599600</v>
       </c>
       <c r="R5" t="n">
-        <v>6923891</v>
+        <v>6923972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902557</v>
+        <v>124902430</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599750</v>
+        <v>599723</v>
       </c>
       <c r="R2" t="n">
-        <v>6923919</v>
+        <v>6923906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902430</v>
+        <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,30 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599723</v>
+        <v>599600</v>
       </c>
       <c r="R3" t="n">
-        <v>6923906</v>
+        <v>6923972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1029,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901243</v>
+        <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1050,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,7 +1070,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599600</v>
+        <v>599750</v>
       </c>
       <c r="R5" t="n">
-        <v>6923972</v>
+        <v>6923919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124901243</v>
+        <v>124902196</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,10 +824,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599600</v>
+        <v>599743</v>
       </c>
       <c r="R3" t="n">
-        <v>6923972</v>
+        <v>6923891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +900,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902196</v>
+        <v>124902557</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +928,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -946,14 +945,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599743</v>
+        <v>599750</v>
       </c>
       <c r="R4" t="n">
-        <v>6923891</v>
+        <v>6923919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902557</v>
+        <v>124901243</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,16 +1045,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,7 +1065,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599750</v>
+        <v>599600</v>
       </c>
       <c r="R5" t="n">
-        <v>6923919</v>
+        <v>6923972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902196</v>
+        <v>124902557</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,14 +824,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599743</v>
+        <v>599750</v>
       </c>
       <c r="R3" t="n">
-        <v>6923891</v>
+        <v>6923919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902557</v>
+        <v>124901243</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,7 +944,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599750</v>
+        <v>599600</v>
       </c>
       <c r="R4" t="n">
-        <v>6923919</v>
+        <v>6923972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901243</v>
+        <v>124902196</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1063,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599600</v>
+        <v>599743</v>
       </c>
       <c r="R5" t="n">
-        <v>6923972</v>
+        <v>6923891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902430</v>
+        <v>124901243</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599723</v>
+        <v>599600</v>
       </c>
       <c r="R2" t="n">
-        <v>6923906</v>
+        <v>6923972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -908,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901243</v>
+        <v>124902196</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,10 +947,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599600</v>
+        <v>599743</v>
       </c>
       <c r="R4" t="n">
-        <v>6923972</v>
+        <v>6923891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902196</v>
+        <v>124902430</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,35 +1047,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599743</v>
+        <v>599723</v>
       </c>
       <c r="R5" t="n">
-        <v>6923891</v>
+        <v>6923906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124901243</v>
+        <v>124902557</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599600</v>
+        <v>599750</v>
       </c>
       <c r="R2" t="n">
-        <v>6923972</v>
+        <v>6923919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902557</v>
+        <v>124902196</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,10 +825,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599750</v>
+        <v>599743</v>
       </c>
       <c r="R3" t="n">
-        <v>6923919</v>
+        <v>6923891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902196</v>
+        <v>124901243</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,14 +946,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599743</v>
+        <v>599600</v>
       </c>
       <c r="R4" t="n">
-        <v>6923891</v>
+        <v>6923972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,12 +1023,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901243</v>
+        <v>124902430</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +925,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599600</v>
+        <v>599723</v>
       </c>
       <c r="R4" t="n">
-        <v>6923972</v>
+        <v>6923906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902430</v>
+        <v>124901243</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,30 +1041,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599723</v>
+        <v>599600</v>
       </c>
       <c r="R5" t="n">
-        <v>6923906</v>
+        <v>6923972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902557</v>
+        <v>124902430</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599750</v>
+        <v>599723</v>
       </c>
       <c r="R2" t="n">
-        <v>6923919</v>
+        <v>6923906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902430</v>
+        <v>124901243</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +924,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599723</v>
+        <v>599600</v>
       </c>
       <c r="R4" t="n">
-        <v>6923906</v>
+        <v>6923972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +1022,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901243</v>
+        <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1050,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,7 +1070,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599600</v>
+        <v>599750</v>
       </c>
       <c r="R5" t="n">
-        <v>6923972</v>
+        <v>6923919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,12 +1139,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902430</v>
+        <v>124902557</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599723</v>
+        <v>599750</v>
       </c>
       <c r="R2" t="n">
-        <v>6923906</v>
+        <v>6923919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902196</v>
+        <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,14 +825,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599743</v>
+        <v>599600</v>
       </c>
       <c r="R3" t="n">
-        <v>6923891</v>
+        <v>6923972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901243</v>
+        <v>124902430</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,31 +926,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599600</v>
+        <v>599723</v>
       </c>
       <c r="R4" t="n">
-        <v>6923972</v>
+        <v>6923906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902557</v>
+        <v>124902196</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,10 +1063,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599750</v>
+        <v>599743</v>
       </c>
       <c r="R5" t="n">
-        <v>6923919</v>
+        <v>6923891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902557</v>
+        <v>124902430</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599750</v>
+        <v>599723</v>
       </c>
       <c r="R2" t="n">
-        <v>6923919</v>
+        <v>6923906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124901243</v>
+        <v>124902557</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +827,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599600</v>
+        <v>599750</v>
       </c>
       <c r="R3" t="n">
-        <v>6923972</v>
+        <v>6923919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902430</v>
+        <v>124901243</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,30 +920,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599723</v>
+        <v>599600</v>
       </c>
       <c r="R4" t="n">
-        <v>6923906</v>
+        <v>6923972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,12 +1018,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>124902196</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>56828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902430</v>
+        <v>124902557</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599723</v>
+        <v>599750</v>
       </c>
       <c r="R2" t="n">
-        <v>6923906</v>
+        <v>6923919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902557</v>
+        <v>124902196</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>56828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,10 +825,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599750</v>
+        <v>599743</v>
       </c>
       <c r="R3" t="n">
-        <v>6923919</v>
+        <v>6923891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1030,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902196</v>
+        <v>124902430</v>
       </c>
       <c r="B5" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,35 +1047,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599743</v>
+        <v>599723</v>
       </c>
       <c r="R5" t="n">
-        <v>6923891</v>
+        <v>6923906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902557</v>
+        <v>124902430</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599750</v>
+        <v>599723</v>
       </c>
       <c r="R2" t="n">
-        <v>6923919</v>
+        <v>6923906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902196</v>
+        <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,14 +814,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599743</v>
+        <v>599600</v>
       </c>
       <c r="R3" t="n">
-        <v>6923891</v>
+        <v>6923972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (över 60 st) på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,27 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901243</v>
+        <v>124902196</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,16 +914,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -946,10 +931,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599600</v>
+        <v>599743</v>
       </c>
       <c r="R4" t="n">
-        <v>6923972</v>
+        <v>6923891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack (över 60 st) på tall</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,54 +1007,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902430</v>
+        <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599723</v>
+        <v>599750</v>
       </c>
       <c r="R5" t="n">
-        <v>6923906</v>
+        <v>6923919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>124902557</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902430</v>
+        <v>124902557</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599723</v>
+        <v>599750</v>
       </c>
       <c r="R2" t="n">
-        <v>6923906</v>
+        <v>6923919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +790,7 @@
         <v>124901243</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124902196</v>
+        <v>124902509</v>
       </c>
       <c r="B4" t="n">
-        <v>56828</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,14 +932,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599743</v>
+        <v>599754</v>
       </c>
       <c r="R4" t="n">
-        <v>6923891</v>
+        <v>6923921</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,27 +1021,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902557</v>
+        <v>124902196</v>
       </c>
       <c r="B5" t="n">
-        <v>57681</v>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,10 +1049,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599750</v>
+        <v>599743</v>
       </c>
       <c r="R5" t="n">
-        <v>6923919</v>
+        <v>6923891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1134,460 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124901624</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>599703</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6923832</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124901767</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599748</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6923842</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124901921</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>599742</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6923857</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124902430</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599723</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6923906</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27950-2022 artfynd.xlsx
+++ b/artfynd/A 27950-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902509</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902196</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901624</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901921</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1588,8 +1628,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902430</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>